--- a/uploads/Impianti Tri Star.xlsx
+++ b/uploads/Impianti Tri Star.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GREEN ENERBRAS ONE SCSp\BRASILE\TRI STAR ENERGY LTDA (GP)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Edoardo\.gemini\antigravity\scratch\GREEN_ENERBRAS\uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6B5ED4C-C262-49DF-BF7E-62C5DBDE5837}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79CC080F-5C30-40F1-B2ED-A7FCD45EABE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{91615A55-A681-40AF-8FA3-823A9DFB907D}"/>
   </bookViews>
@@ -162,9 +162,6 @@
     <t>SOMBRA FLORESTA</t>
   </si>
   <si>
-    <t>FINITO - IN ATTESA DI AUTORIZZAZIONE COSERN</t>
-  </si>
-  <si>
     <t>NO</t>
   </si>
   <si>
@@ -322,6 +319,9 @@
   </si>
   <si>
     <t>FOTUS ENERGIA SOLAR LTDA</t>
+  </si>
+  <si>
+    <t>COMPLETATO - ATTESA AUTORIZZAZIONE COSERN</t>
   </si>
 </sst>
 </file>
@@ -841,31 +841,31 @@
         <v>37</v>
       </c>
       <c r="T1" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="U1" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="V1" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="W1" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="X1" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="Y1" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="Z1" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="Z1" s="5" t="s">
-        <v>71</v>
-      </c>
       <c r="AA1" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="AB1" s="5" t="s">
         <v>88</v>
-      </c>
-      <c r="AB1" s="5" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="2" spans="1:28" s="11" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -873,7 +873,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C2" s="10" t="s">
         <v>24</v>
@@ -882,13 +882,13 @@
         <v>3</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F2" s="10" t="s">
         <v>30</v>
       </c>
       <c r="G2" s="14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H2" s="10">
         <v>120000</v>
@@ -897,7 +897,7 @@
         <v>8</v>
       </c>
       <c r="J2" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K2" s="14" t="s">
         <v>32</v>
@@ -927,13 +927,13 @@
         <v>41</v>
       </c>
       <c r="T2" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="U2" s="10"/>
       <c r="V2" s="10"/>
       <c r="W2" s="14"/>
       <c r="X2" s="9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Y2" s="9">
         <v>60</v>
@@ -947,7 +947,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C3" s="10" t="s">
         <v>24</v>
@@ -956,13 +956,13 @@
         <v>3</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F3" s="10" t="s">
         <v>30</v>
       </c>
       <c r="G3" s="14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H3" s="10">
         <v>120000</v>
@@ -971,7 +971,7 @@
         <v>8</v>
       </c>
       <c r="J3" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K3" s="14" t="s">
         <v>32</v>
@@ -1001,13 +1001,13 @@
         <v>40</v>
       </c>
       <c r="T3" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="U3" s="10"/>
       <c r="V3" s="10"/>
       <c r="W3" s="14"/>
       <c r="X3" s="9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="Y3" s="9">
         <v>30</v>
@@ -1016,12 +1016,12 @@
         <v>2605206863</v>
       </c>
     </row>
-    <row r="4" spans="1:28" s="11" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:28" s="11" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" s="9">
         <v>3</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C4" s="10" t="s">
         <v>25</v>
@@ -1030,7 +1030,7 @@
         <v>14</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F4" s="10" t="s">
         <v>19</v>
@@ -1045,7 +1045,7 @@
         <v>8</v>
       </c>
       <c r="J4" s="10" t="s">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="K4" s="14" t="s">
         <v>33</v>
@@ -1066,39 +1066,39 @@
         <v>450</v>
       </c>
       <c r="Q4" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="R4" s="8"/>
       <c r="T4" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="U4" s="10"/>
       <c r="V4" s="10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="W4" s="14" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="X4" s="9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Y4" s="9">
         <v>60</v>
       </c>
       <c r="Z4" s="9"/>
       <c r="AA4" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AB4" s="11" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="5" spans="1:28" s="11" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="5" spans="1:28" s="11" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A5" s="9">
         <v>4</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C5" s="10" t="s">
         <v>25</v>
@@ -1107,7 +1107,7 @@
         <v>14</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F5" s="10" t="s">
         <v>20</v>
@@ -1122,7 +1122,7 @@
         <v>8</v>
       </c>
       <c r="J5" s="10" t="s">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="K5" s="14" t="s">
         <v>33</v>
@@ -1143,39 +1143,39 @@
         <v>450</v>
       </c>
       <c r="Q5" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="R5" s="8"/>
       <c r="T5" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="U5" s="10"/>
       <c r="V5" s="10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="W5" s="14" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="X5" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y5" s="9">
         <v>60</v>
       </c>
       <c r="Z5" s="9"/>
       <c r="AA5" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AB5" s="11" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="6" spans="1:28" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="6" spans="1:28" s="11" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" s="9">
         <v>5</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C6" s="10" t="s">
         <v>26</v>
@@ -1184,7 +1184,7 @@
         <v>21</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F6" s="10" t="s">
         <v>22</v>
@@ -1199,7 +1199,7 @@
         <v>8</v>
       </c>
       <c r="J6" s="10" t="s">
-        <v>58</v>
+        <v>95</v>
       </c>
       <c r="K6" s="14" t="s">
         <v>34</v>
@@ -1220,29 +1220,29 @@
         <v>450</v>
       </c>
       <c r="Q6" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="R6" s="9"/>
       <c r="T6" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="U6" s="10"/>
       <c r="V6" s="10"/>
       <c r="W6" s="14"/>
       <c r="X6" s="9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="Y6" s="9">
         <v>60</v>
       </c>
       <c r="Z6" s="9"/>
     </row>
-    <row r="7" spans="1:28" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:28" s="11" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A7" s="9">
         <v>6</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C7" s="10" t="s">
         <v>26</v>
@@ -1251,7 +1251,7 @@
         <v>21</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F7" s="10" t="s">
         <v>28</v>
@@ -1266,7 +1266,7 @@
         <v>8</v>
       </c>
       <c r="J7" s="10" t="s">
-        <v>58</v>
+        <v>95</v>
       </c>
       <c r="K7" s="14" t="s">
         <v>34</v>
@@ -1287,17 +1287,17 @@
         <v>450</v>
       </c>
       <c r="Q7" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="R7" s="9"/>
       <c r="T7" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="U7" s="10"/>
       <c r="V7" s="10"/>
       <c r="W7" s="14"/>
       <c r="X7" s="9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="Y7" s="9">
         <v>60</v>
@@ -1309,7 +1309,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C8" s="10" t="s">
         <v>24</v>
@@ -1318,13 +1318,13 @@
         <v>3</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G8" s="14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H8" s="10">
         <v>122700</v>
@@ -1333,7 +1333,7 @@
         <v>8</v>
       </c>
       <c r="J8" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K8" s="14" t="s">
         <v>32</v>
@@ -1360,10 +1360,10 @@
         <v>46156</v>
       </c>
       <c r="S8" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="T8" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="U8" s="10">
         <f>75/2</f>
@@ -1372,7 +1372,7 @@
       <c r="V8" s="10"/>
       <c r="W8" s="14"/>
       <c r="X8" s="9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="Y8" s="9">
         <v>60</v>
@@ -1386,7 +1386,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C9" s="10" t="s">
         <v>24</v>
@@ -1395,13 +1395,13 @@
         <v>3</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G9" s="14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H9" s="10">
         <v>122700</v>
@@ -1410,7 +1410,7 @@
         <v>8</v>
       </c>
       <c r="J9" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K9" s="14" t="s">
         <v>32</v>
@@ -1440,7 +1440,7 @@
         <v>39</v>
       </c>
       <c r="T9" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="U9" s="10">
         <v>37.5</v>
@@ -1448,7 +1448,7 @@
       <c r="V9" s="10"/>
       <c r="W9" s="14"/>
       <c r="X9" s="9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="Y9" s="9">
         <v>60</v>
@@ -1462,7 +1462,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C10" s="10" t="s">
         <v>24</v>
@@ -1471,13 +1471,13 @@
         <v>3</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F10" s="10" t="s">
         <v>30</v>
       </c>
       <c r="G10" s="14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H10" s="10">
         <v>20000</v>
@@ -1486,7 +1486,7 @@
         <v>8</v>
       </c>
       <c r="J10" s="10" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="K10" s="14" t="s">
         <v>32</v>
@@ -1516,13 +1516,13 @@
         <v>41</v>
       </c>
       <c r="T10" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="U10" s="10"/>
       <c r="V10" s="10"/>
       <c r="W10" s="14"/>
       <c r="X10" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="Y10" s="9">
         <v>60</v>
@@ -1536,7 +1536,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C11" s="10" t="s">
         <v>24</v>
@@ -1545,13 +1545,13 @@
         <v>3</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F11" s="10" t="s">
         <v>30</v>
       </c>
       <c r="G11" s="14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H11" s="10">
         <v>20000</v>
@@ -1560,7 +1560,7 @@
         <v>8</v>
       </c>
       <c r="J11" s="10" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="K11" s="14" t="s">
         <v>32</v>
@@ -1590,13 +1590,13 @@
         <v>41</v>
       </c>
       <c r="T11" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="U11" s="10"/>
       <c r="V11" s="10"/>
       <c r="W11" s="14"/>
       <c r="X11" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Y11" s="9">
         <v>60</v>
@@ -1608,7 +1608,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C12" s="10" t="s">
         <v>24</v>
@@ -1617,13 +1617,13 @@
         <v>3</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F12" s="10" t="s">
         <v>30</v>
       </c>
       <c r="G12" s="14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H12" s="10">
         <v>20000</v>
@@ -1632,7 +1632,7 @@
         <v>8</v>
       </c>
       <c r="J12" s="10" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="K12" s="14" t="s">
         <v>32</v>
@@ -1662,13 +1662,13 @@
         <v>41</v>
       </c>
       <c r="T12" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="U12" s="10"/>
       <c r="V12" s="10"/>
       <c r="W12" s="14"/>
       <c r="X12" s="9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Y12" s="9">
         <v>60</v>
@@ -1680,7 +1680,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C13" s="10" t="s">
         <v>24</v>
@@ -1689,13 +1689,13 @@
         <v>3</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F13" s="10" t="s">
         <v>30</v>
       </c>
       <c r="G13" s="14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H13" s="10">
         <v>20000</v>
@@ -1704,7 +1704,7 @@
         <v>8</v>
       </c>
       <c r="J13" s="10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="K13" s="14" t="s">
         <v>32</v>
@@ -1734,13 +1734,13 @@
         <v>41</v>
       </c>
       <c r="T13" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="U13" s="10"/>
       <c r="V13" s="10"/>
       <c r="W13" s="14"/>
       <c r="X13" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="Y13" s="9">
         <v>60</v>
